--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96738</v>
+        <v>96744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96744</v>
+        <v>96747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127748687</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96747</v>
+        <v>96755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127748687</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96755</v>
+        <v>96756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96756</v>
+        <v>96757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96757</v>
+        <v>96758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127748687</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127748723</v>
       </c>
       <c r="B2" t="n">
-        <v>96766</v>
+        <v>96859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127748687</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,6 +888,1158 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129030242</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562592</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6453740</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129029178</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562503</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453725</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129030182</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562582</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453783</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129029958</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562570</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6453767</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129030138</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562561</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453787</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129029224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562515</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6453749</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många fläckar på låga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129029116</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562494</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6453734</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129029989</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562564</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6453759</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett flertal, två växtplatser nära varandra</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129030196</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562582</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6453783</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129029069</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79648</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562443</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6453782</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129030087</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562569</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6453787</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>79653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>91520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,39 +2593,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2668,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57564</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57564</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>79653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2281,7 +2281,7 @@
         <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,37 +2690,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2765,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57564</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92849</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>92854</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2281,7 +2281,7 @@
         <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>129101979</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,39 +2593,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2668,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>129101881</v>
       </c>
       <c r="B24" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57564</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57564</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>92857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92854</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1209,42 +1209,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R7" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,12 +1286,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1314,38 +1316,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R8" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,18 +1397,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,54 +2042,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2097,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,6 +2130,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,30 +2160,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2211,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2244,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,38 +2271,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2367,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,7 +2587,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
         <v>98659</v>
@@ -2632,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,37 +2694,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2769,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1209,38 +1209,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R7" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,18 +1290,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,42 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R8" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,12 +1391,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,38 +2042,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101888</v>
+        <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2081,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562714</v>
+        <v>562627</v>
       </c>
       <c r="R15" t="n">
-        <v>6453593</v>
+        <v>6453628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,7 +2146,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2149,54 +2164,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2204,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R16" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,6 +2252,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2164,38 +2164,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R16" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2260,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2271,46 +2278,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101841</v>
+        <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2318,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562643</v>
+        <v>562714</v>
       </c>
       <c r="R17" t="n">
-        <v>6453652</v>
+        <v>6453593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,6 +2366,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2587,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,7 +2690,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
         <v>98659</v>
@@ -2733,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129030182</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>129030138</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>129030087</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129101841</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,38 +2053,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2097,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562643</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453652</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2129,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,46 +2156,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2211,10 +2195,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562714</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2235,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,6 +2244,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2278,38 +2263,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101956</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562627</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2367,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>129101979</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101863</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562744</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,39 +2593,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2668,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>129101881</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57564</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>129119555</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129119571</v>
       </c>
       <c r="B37" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101863</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562744</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453652</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,37 +2690,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2765,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101917</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562655</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453614</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57566</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,30 +2053,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2089,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R15" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,38 +2164,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2195,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R16" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,7 +2260,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2263,54 +2278,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2318,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R17" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,6 +2366,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57566</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92864</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>92871</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129030182</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>129030138</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>129030087</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>129101979</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,39 +2593,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2668,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>129101881</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57566</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>129119555</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129119571</v>
       </c>
       <c r="B37" t="n">
-        <v>57719</v>
+        <v>57721</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1209,42 +1209,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R7" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,12 +1286,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1314,38 +1316,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R8" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,18 +1397,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,37 +2690,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2765,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2587,39 +2587,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
         <v>98678</v>
@@ -2729,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,54 +2042,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2097,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,6 +2130,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,30 +2160,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2211,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2244,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,38 +2271,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2367,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>92859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,38 +2042,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101888</v>
+        <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2081,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562714</v>
+        <v>562627</v>
       </c>
       <c r="R15" t="n">
-        <v>6453593</v>
+        <v>6453628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,7 +2146,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2149,54 +2164,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2204,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R16" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,6 +2252,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>92860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92859</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129101841</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,38 +2053,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2097,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562643</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453652</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2129,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,7 +2159,7 @@
         <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,30 +2274,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R17" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,37 +2690,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2765,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92860</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>92860</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,38 +1209,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R7" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,18 +1290,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,42 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R8" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,12 +1391,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>79662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2159,7 +2159,7 @@
         <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>129101979</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,39 +2587,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>129101881</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79662</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>79662</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79662</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2156,38 +2156,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101888</v>
+        <v>129101956</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2195,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562714</v>
+        <v>562627</v>
       </c>
       <c r="R16" t="n">
-        <v>6453593</v>
+        <v>6453628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,7 +2260,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2263,54 +2278,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2318,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R17" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,6 +2366,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>129101979</v>
       </c>
       <c r="B18" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>129101881</v>
       </c>
       <c r="B24" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>92865</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92863</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,30 +2053,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2089,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R15" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101956</v>
+        <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,38 +2175,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562627</v>
+        <v>562643</v>
       </c>
       <c r="R16" t="n">
-        <v>6453628</v>
+        <v>6453652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,7 +2281,7 @@
         <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,37 +2486,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101971</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562592</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453629</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,39 +2589,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101869</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>91549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562761</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,42 +1209,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R7" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,12 +1286,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1314,38 +1316,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R8" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,18 +1397,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,54 +2042,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2097,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,6 +2130,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101956</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,30 +2160,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2211,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562627</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2244,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2278,38 +2271,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2367,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2486,39 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101971</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562592</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453629</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,37 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101869</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>91549</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562761</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453658</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>92870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1209,38 +1209,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129029958</v>
+        <v>129030138</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562570</v>
+        <v>562561</v>
       </c>
       <c r="R7" t="n">
-        <v>6453767</v>
+        <v>6453787</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,18 +1290,12 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,42 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129030138</v>
+        <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562561</v>
+        <v>562570</v>
       </c>
       <c r="R8" t="n">
-        <v>6453787</v>
+        <v>6453767</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,12 +1391,18 @@
           <t>2025-09-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2042,38 +2042,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101888</v>
+        <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2081,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562714</v>
+        <v>562627</v>
       </c>
       <c r="R15" t="n">
-        <v>6453593</v>
+        <v>6453628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,7 +2146,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2149,54 +2164,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101956</v>
+        <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2204,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562627</v>
+        <v>562714</v>
       </c>
       <c r="R16" t="n">
-        <v>6453628</v>
+        <v>6453593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,6 +2252,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2486,37 +2486,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129101917</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562655</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,39 +2593,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2668,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,38 +2700,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2729,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>92870</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92870</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129029069</v>
+        <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562443</v>
+        <v>562582</v>
       </c>
       <c r="R12" t="n">
-        <v>6453782</v>
+        <v>6453783</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129030196</v>
+        <v>129029069</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562582</v>
+        <v>562443</v>
       </c>
       <c r="R13" t="n">
-        <v>6453783</v>
+        <v>6453782</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2486,38 +2486,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101917</v>
+        <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562655</v>
+        <v>562761</v>
       </c>
       <c r="R19" t="n">
-        <v>6453614</v>
+        <v>6453658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,7 +2587,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
         <v>98724</v>
@@ -2632,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,37 +2694,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101869</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562761</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453658</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2769,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129030242</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>129029178</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129029958</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129029224</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129029116</v>
       </c>
       <c r="B10" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129029989</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129030196</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,38 +2164,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R16" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2260,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2271,46 +2278,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101841</v>
+        <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2318,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562643</v>
+        <v>562714</v>
       </c>
       <c r="R17" t="n">
-        <v>6453652</v>
+        <v>6453593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,6 +2366,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>129101869</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>129101917</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129101863</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>129101904</v>
       </c>
       <c r="B23" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>129101789</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129101968</v>
       </c>
       <c r="B26" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>129101824</v>
       </c>
       <c r="B27" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>129119157</v>
       </c>
       <c r="B31" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129119313</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92870</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
         <v>129119475</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2164,46 +2164,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101888</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2211,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562714</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,6 +2252,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2278,38 +2271,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,7 +2367,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2587,38 +2587,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129101971</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562592</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,7 +2690,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>129101917</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2733,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562655</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453614</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,39 +2797,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101863</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562592</v>
+        <v>562744</v>
       </c>
       <c r="R22" t="n">
-        <v>6453629</v>
+        <v>6453652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2164,38 +2164,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101888</v>
+        <v>129101841</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562714</v>
+        <v>562643</v>
       </c>
       <c r="R16" t="n">
-        <v>6453593</v>
+        <v>6453652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2260,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2271,46 +2278,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101841</v>
+        <v>129101888</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2318,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562643</v>
+        <v>562714</v>
       </c>
       <c r="R17" t="n">
-        <v>6453652</v>
+        <v>6453593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Revirparet i sitt revir</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,6 +2366,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,28 +3531,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,13 +3605,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3623,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,35 +3645,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3708,17 +3712,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2587,39 +2587,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101971</v>
+        <v>129101917</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2627,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562592</v>
+        <v>562655</v>
       </c>
       <c r="R20" t="n">
-        <v>6453629</v>
+        <v>6453614</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101917</v>
+        <v>129101863</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2729,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562655</v>
+        <v>562744</v>
       </c>
       <c r="R21" t="n">
-        <v>6453614</v>
+        <v>6453652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,38 +2801,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101863</v>
+        <v>129101971</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562744</v>
+        <v>562592</v>
       </c>
       <c r="R22" t="n">
-        <v>6453652</v>
+        <v>6453629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101989</v>
+        <v>129101846</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,35 +3531,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3567,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562526</v>
+        <v>562691</v>
       </c>
       <c r="R29" t="n">
-        <v>6453663</v>
+        <v>6453632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,17 +3598,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101846</v>
+        <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,28 +3634,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562691</v>
+        <v>562526</v>
       </c>
       <c r="R30" t="n">
-        <v>6453632</v>
+        <v>6453663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,13 +3708,17 @@
           <t>2025-10-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4063,38 +4063,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4170,41 +4168,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4212,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4063,41 +4063,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119625</v>
+        <v>129119479</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4105,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562492</v>
+        <v>562561</v>
       </c>
       <c r="R34" t="n">
-        <v>6453762</v>
+        <v>6453696</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4168,38 +4170,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119479</v>
+        <v>129119625</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562561</v>
+        <v>562492</v>
       </c>
       <c r="R35" t="n">
-        <v>6453696</v>
+        <v>6453762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4497,6 +4497,647 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131704608</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Åtvid, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562760</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6453569</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Tätt hårt mjöl i ovala, ca 3 mm breda, gångar</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131710269</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97900</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562630</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6453623</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I gammalt kvartsbrott</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131704629</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>353</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Åtvid, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>562760</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6453569</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131712357</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>562692</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6453824</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131711301</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Åtvid, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>562760</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6453569</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97900</v>
+        <v>97901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57739</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>131704608</v>
       </c>
       <c r="B38" t="n">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97901</v>
+        <v>97902</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78926</v>
+        <v>78927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>131711301</v>
       </c>
       <c r="B42" t="n">
-        <v>4779</v>
+        <v>4780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97902</v>
+        <v>97905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78927</v>
+        <v>78930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>129101956</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>129101989</v>
       </c>
       <c r="B30" t="n">
-        <v>57743</v>
+        <v>57745</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97905</v>
+        <v>97911</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4502,7 +4502,7 @@
         <v>131704608</v>
       </c>
       <c r="B38" t="n">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97911</v>
+        <v>97914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78932</v>
+        <v>78935</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>131711301</v>
       </c>
       <c r="B42" t="n">
-        <v>4780</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97914</v>
+        <v>97919</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97919</v>
+        <v>97921</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>131712357</v>
       </c>
       <c r="B41" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -4629,7 +4629,7 @@
         <v>131710269</v>
       </c>
       <c r="B39" t="n">
-        <v>97962</v>
+        <v>97965</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>131704629</v>
       </c>
       <c r="B40" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5138,6 +5138,127 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132469320</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slättkärrs barrskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>562708</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6453866</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,6 +5258,116 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132652449</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96542</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>210</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Alserum, Åtvidabergs kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>562763</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6453613</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tilde Tängerstad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tilde Tängerstad, Emil Ideskär, William Rosén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
+          <t>Tilde Tängerstad, Emil Ideskär, Fanny Nyberg, William Rosén, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad, Emil Ideskär, Fanny Nyberg, William Rosén, Gabriella Fjellander</t>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91930</v>
+        <v>91931</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96554</v>
+        <v>96555</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96555</v>
+        <v>96557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -5143,7 +5143,7 @@
         <v>132469320</v>
       </c>
       <c r="B43" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>132652449</v>
       </c>
       <c r="B44" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127748723</v>
+        <v>132652449</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alserum/Tolen, Ög</t>
+          <t>Alserum, Åtvidabergs kommun, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562580</v>
+        <v>562763</v>
       </c>
       <c r="R2" t="n">
-        <v>6453809</v>
+        <v>6453613</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,19 +752,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -765,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Tilde Tängerstad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Tilde Tängerstad, Emil Ideskär, William Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127748687</v>
+        <v>131704629</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,53 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ekliden/Alserum, Ög</t>
+          <t>Alserums tallskog, Åtvid, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562454</v>
+        <v>562760</v>
       </c>
       <c r="R3" t="n">
-        <v>6453757</v>
+        <v>6453569</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,54 +881,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>William Rosén, Fanny Nyberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129030242</v>
+        <v>129029224</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562592</v>
+        <v>562515</v>
       </c>
       <c r="R4" t="n">
-        <v>6453740</v>
+        <v>6453749</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett flertal</t>
+          <t>Många fläckar på låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,38 +1023,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129029178</v>
+        <v>129030196</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562503</v>
+        <v>562582</v>
       </c>
       <c r="R5" t="n">
-        <v>6453725</v>
+        <v>6453783</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,11 +1097,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129030182</v>
+        <v>129101853</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,45 +1135,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562582</v>
+        <v>562737</v>
       </c>
       <c r="R6" t="n">
-        <v>6453783</v>
+        <v>6453660</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,12 +1192,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129030138</v>
+        <v>129101869</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,45 +1236,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562561</v>
+        <v>562761</v>
       </c>
       <c r="R7" t="n">
-        <v>6453787</v>
+        <v>6453658</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,6 +1307,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1314,52 +1326,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129029958</v>
+        <v>129119157</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562570</v>
+        <v>562471</v>
       </c>
       <c r="R8" t="n">
-        <v>6453767</v>
+        <v>6453750</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,17 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett flertal</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129029224</v>
+        <v>129119172</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,17 +1461,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562515</v>
+        <v>562451</v>
       </c>
       <c r="R9" t="n">
-        <v>6453749</v>
+        <v>6453710</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,17 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många fläckar på låga</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,48 +1528,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129029116</v>
+        <v>127748723</v>
       </c>
       <c r="B10" t="n">
-        <v>91574</v>
+        <v>97394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserum/Tolen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562494</v>
+        <v>562580</v>
       </c>
       <c r="R10" t="n">
-        <v>6453734</v>
+        <v>6453809</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1595,19 +1597,19 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
@@ -1616,64 +1618,70 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129029989</v>
+        <v>132469069</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>96512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Bergväggar vid Alserums tallskog, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562564</v>
+        <v>562729</v>
       </c>
       <c r="R11" t="n">
-        <v>6453759</v>
+        <v>6453546</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1697,17 +1705,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ett flertal, två växtplatser nära varandra</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1716,70 +1729,76 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129030196</v>
+        <v>132469191</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>96501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Bergväggar vid Alserums tallskog, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562582</v>
+        <v>562729</v>
       </c>
       <c r="R12" t="n">
-        <v>6453783</v>
+        <v>6453546</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,12 +1822,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,70 +1846,76 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129029069</v>
+        <v>132469045</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>96306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2779</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Bergväggar vid Alserums tallskog, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562443</v>
+        <v>562729</v>
       </c>
       <c r="R13" t="n">
-        <v>6453782</v>
+        <v>6453546</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,12 +1939,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,75 +1963,76 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129030087</v>
+        <v>131710143</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alserum/Kävelsbo, Ög</t>
+          <t>Alserums tallskog, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562569</v>
+        <v>562663</v>
       </c>
       <c r="R14" t="n">
-        <v>6453787</v>
+        <v>6453576</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2010,12 +2056,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,26 +2082,46 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129101956</v>
+        <v>129029116</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,57 +2129,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562627</v>
+        <v>562494</v>
       </c>
       <c r="R15" t="n">
-        <v>6453628</v>
+        <v>6453734</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2127,17 +2186,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,6 +2200,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129101841</v>
+        <v>129101767</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,35 +2230,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2211,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562643</v>
+        <v>562723</v>
       </c>
       <c r="R16" t="n">
-        <v>6453652</v>
+        <v>6453899</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,17 +2299,13 @@
           <t>2025-10-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Revirparet i sitt revir</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2278,38 +2324,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129101888</v>
+        <v>129101904</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2317,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562714</v>
+        <v>562658</v>
       </c>
       <c r="R17" t="n">
-        <v>6453593</v>
+        <v>6453607</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,11 +2398,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129101979</v>
+        <v>129101966</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,24 +2436,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2423,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562578</v>
+        <v>562585</v>
       </c>
       <c r="R18" t="n">
-        <v>6453662</v>
+        <v>6453610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,6 +2503,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En gammal fruktkropp som ramlade av trädet och ligger vid stambasen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129101869</v>
+        <v>129119461</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562761</v>
+        <v>562561</v>
       </c>
       <c r="R19" t="n">
-        <v>6453658</v>
+        <v>6453616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,12 +2603,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,38 +2636,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129101917</v>
+        <v>129119467</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2626,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562655</v>
+        <v>562551</v>
       </c>
       <c r="R20" t="n">
-        <v>6453614</v>
+        <v>6453617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,17 +2704,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,49 +2737,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129101863</v>
+        <v>132469320</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>91995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Slättkärrs barrskog, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562744</v>
+        <v>562708</v>
       </c>
       <c r="R21" t="n">
-        <v>6453652</v>
+        <v>6453866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,17 +2816,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,29 +2840,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg, Emil Ideskär, Tilde Tängerstad, Gabriella Fjellander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129101971</v>
+        <v>129101968</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,28 +2869,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2904,10 +2959,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129101904</v>
+        <v>129101824</v>
       </c>
       <c r="B23" t="n">
-        <v>91574</v>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2915,24 +2970,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -2942,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562658</v>
+        <v>562633</v>
       </c>
       <c r="R23" t="n">
-        <v>6453607</v>
+        <v>6453668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129101881</v>
+        <v>129119200</v>
       </c>
       <c r="B24" t="n">
-        <v>79663</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,21 +3075,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3043,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562784</v>
+        <v>562468</v>
       </c>
       <c r="R24" t="n">
-        <v>6453660</v>
+        <v>6453690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3073,12 +3132,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,38 +3165,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129101789</v>
+        <v>129119625</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3145,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562721</v>
+        <v>562492</v>
       </c>
       <c r="R25" t="n">
-        <v>6453845</v>
+        <v>6453762</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3175,17 +3237,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3270,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129101968</v>
+        <v>129029069</v>
       </c>
       <c r="B26" t="n">
-        <v>91517</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,17 +3304,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562592</v>
+        <v>562443</v>
       </c>
       <c r="R26" t="n">
-        <v>6453629</v>
+        <v>6453782</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3281,12 +3338,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3314,10 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129101824</v>
+        <v>129101881</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,28 +3382,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3356,10 +3409,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562633</v>
+        <v>562784</v>
       </c>
       <c r="R27" t="n">
-        <v>6453668</v>
+        <v>6453660</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,7 +3475,7 @@
         <v>129101958</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3520,39 +3573,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129101846</v>
+        <v>129101979</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3560,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562691</v>
+        <v>562578</v>
       </c>
       <c r="R29" t="n">
-        <v>6453632</v>
+        <v>6453662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,46 +3674,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129101989</v>
+        <v>129119470</v>
       </c>
       <c r="B30" t="n">
-        <v>57745</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3670,10 +3712,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562526</v>
+        <v>562551</v>
       </c>
       <c r="R30" t="n">
-        <v>6453663</v>
+        <v>6453617</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3700,17 +3742,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3719,6 +3756,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3737,51 +3775,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129119157</v>
+        <v>129030087</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562471</v>
+        <v>562569</v>
       </c>
       <c r="R31" t="n">
-        <v>6453750</v>
+        <v>6453787</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,12 +3848,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,7 +3862,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3838,64 +3880,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129119555</v>
+        <v>129030138</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562588</v>
+        <v>562561</v>
       </c>
       <c r="R32" t="n">
-        <v>6453695</v>
+        <v>6453787</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3919,17 +3953,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Revirparet inom huvuddelen av reviret.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3956,52 +3985,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129119313</v>
+        <v>129030182</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserum/Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562517</v>
+        <v>562582</v>
       </c>
       <c r="R33" t="n">
-        <v>6453686</v>
+        <v>6453783</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,17 +4058,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4072,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4063,38 +4090,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129119479</v>
+        <v>129101956</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4102,10 +4145,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562561</v>
+        <v>562627</v>
       </c>
       <c r="R34" t="n">
-        <v>6453696</v>
+        <v>6453628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4132,17 +4175,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den drygt 140 åriga talldominerade kontinuitetsskogen som är ca 180 till 200 år gamla  på hällmarken utgör en viktig del av spillkråkans revir. Vissa tallar är ca 250 år gamla och vissa av dem har hästmyror vilka är faforitföda åt spillkråkan.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,7 +4194,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4170,55 +4212,58 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129119625</v>
+        <v>131712357</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Alserum-Kävelsbo, Ög</t>
+          <t>Alserums tallskog, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562492</v>
+        <v>562692</v>
       </c>
       <c r="R35" t="n">
-        <v>6453762</v>
+        <v>6453824</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,12 +4287,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,57 +4311,57 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>William Rosén, Fanny Nyberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129119475</v>
+        <v>129101846</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4314,10 +4369,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562577</v>
+        <v>562691</v>
       </c>
       <c r="R36" t="n">
-        <v>6453634</v>
+        <v>6453632</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4344,17 +4399,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4382,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129119571</v>
+        <v>129101971</v>
       </c>
       <c r="B37" t="n">
-        <v>57721</v>
+        <v>5179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,43 +4443,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102977</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4437,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562629</v>
+        <v>562592</v>
       </c>
       <c r="R37" t="n">
-        <v>6453709</v>
+        <v>6453629</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,12 +4502,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4481,6 +4516,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4499,63 +4535,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131704608</v>
+        <v>129119318</v>
       </c>
       <c r="B38" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Alserums tallskog, Åtvid, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562760</v>
+        <v>562520</v>
       </c>
       <c r="R38" t="n">
-        <v>6453569</v>
+        <v>6453665</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4579,27 +4605,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Tätt hårt mjöl i ovala, ca 3 mm breda, gångar</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4608,57 +4619,62 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>William Rosén, Fanny Nyberg</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131710269</v>
+        <v>131704608</v>
       </c>
       <c r="B39" t="n">
-        <v>97965</v>
+        <v>5497</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224363</v>
+        <v>101410</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4668,17 +4684,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Alserums tallskog, Ög</t>
+          <t>Alserums tallskog, Åtvid, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562630</v>
+        <v>562760</v>
       </c>
       <c r="R39" t="n">
-        <v>6453623</v>
+        <v>6453569</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4707,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4717,12 +4733,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I gammalt kvartsbrott</t>
+          <t>Tätt hårt mjöl i ovala, ca 3 mm breda, gångar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4749,38 +4765,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131704629</v>
+        <v>131711301</v>
       </c>
       <c r="B40" t="n">
-        <v>78983</v>
+        <v>4782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4824,7 +4850,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4834,7 +4860,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,22 +4874,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4881,58 +4907,60 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131712357</v>
+        <v>129101989</v>
       </c>
       <c r="B41" t="n">
-        <v>57136</v>
+        <v>57794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Alserums tallskog, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562692</v>
+        <v>562526</v>
       </c>
       <c r="R41" t="n">
-        <v>6453824</v>
+        <v>6453663</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4956,22 +4984,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Den gamla kontinuitetsskogen utgör en viktig del av sparvugglans revir.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,22 +5009,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>William Rosén, Fanny Nyberg</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131711301</v>
+        <v>129119571</v>
       </c>
       <c r="B42" t="n">
-        <v>4781</v>
+        <v>57947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,52 +5032,57 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>102977</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Alserums tallskog, Åtvid, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562760</v>
+        <v>562629</v>
       </c>
       <c r="R42" t="n">
-        <v>6453569</v>
+        <v>6453709</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5078,22 +5106,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5104,46 +5122,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>William Rosén, Fanny Nyberg</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132469320</v>
+        <v>127748687</v>
       </c>
       <c r="B43" t="n">
-        <v>91939</v>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5151,51 +5149,53 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slättkärrs barrskog, Ög</t>
+          <t>Ekliden/Alserum, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562708</v>
+        <v>562454</v>
       </c>
       <c r="R43" t="n">
-        <v>6453866</v>
+        <v>6453757</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5219,22 +5219,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5249,69 +5239,69 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad, Emil Ideskär, Fanny Nyberg, William Rosén, Gabriella Fjellander</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132652449</v>
+        <v>129101841</v>
       </c>
       <c r="B44" t="n">
-        <v>96564</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>kapslar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Alserum, Åtvidabergs kommun, Ög</t>
+          <t>Alserum-Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562763</v>
+        <v>562643</v>
       </c>
       <c r="R44" t="n">
-        <v>6453613</v>
+        <v>6453652</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5338,12 +5328,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Revirparet i sitt revir</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5352,22 +5347,1653 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tilde Tängerstad, Emil Ideskär, William Rosén</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129119555</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>562588</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6453695</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Revirparet inom huvuddelen av reviret.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129029178</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>562503</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6453725</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129029958</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>562570</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6453767</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129029989</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>562564</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6453759</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ett flertal, två växtplatser nära varandra</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129030242</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Alserum/Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>562592</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6453740</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ett flertal</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129101789</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>562721</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6453845</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129101863</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>562744</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6453652</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129101888</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>562714</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6453593</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129101917</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>562655</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6453614</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129119164</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>562461</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6453714</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129119306</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>562472</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6453695</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129119313</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>562517</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6453686</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129119475</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>562577</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6453634</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129119479</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Alserum-Kävelsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>562561</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6453696</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131710269</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98062</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Alserums tallskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>562630</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6453623</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I gammalt kvartsbrott</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34703-2025 artfynd.xlsx
+++ b/artfynd/A 34703-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132652449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131704629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030196</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101869</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119172</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469069</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469191</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469045</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131710143</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2216,6 +2286,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029116</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101767</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101904</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101966</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2633,6 +2723,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119461</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2734,6 +2829,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119467</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2855,6 +2955,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469320</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2956,6 +3061,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101968</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3061,6 +3171,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101824</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3162,6 +3277,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119200</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3267,6 +3387,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119625</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3368,6 +3493,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029069</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3469,6 +3599,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101881</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3570,6 +3705,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101958</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3671,6 +3811,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101979</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3772,6 +3917,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119470</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3877,6 +4027,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030087</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3982,6 +4137,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030138</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4087,6 +4247,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030182</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4209,6 +4374,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101956</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4326,6 +4496,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131712357</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4429,6 +4604,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101846</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4532,6 +4712,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101971</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4635,6 +4820,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119318</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4762,6 +4952,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131704608</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4904,6 +5099,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131711301</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5018,6 +5218,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101989</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5135,6 +5340,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119571</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5248,6 +5458,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748687</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5362,6 +5577,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101841</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5480,6 +5700,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119555</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5587,6 +5812,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029178</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5694,6 +5924,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029958</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5801,6 +6036,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129029989</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5908,6 +6148,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030242</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6015,6 +6260,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6122,6 +6372,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101863</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6229,6 +6484,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101888</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6336,6 +6596,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101917</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6443,6 +6708,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119164</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6550,6 +6820,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119306</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6657,6 +6932,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119313</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6764,6 +7044,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119475</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6871,6 +7156,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129119479</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6994,8 +7284,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131710269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>